--- a/servers/maze_main_server/conf.d/data/maze_kongfu_hit_move_ratio_v8【迷宫-武力比-怪物被击退几率】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_kongfu_hit_move_ratio_v8【迷宫-武力比-怪物被击退几率】.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C80E7A-8DED-4FE0-9DE3-BF08E5BCB31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14175"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{FE46E8E0-91A0-4197-9582-3C8FD9DC5F24}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_kongfu_hit_move_ratio_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,62 +39,75 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>paipaiworld_config</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>LONG_C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>INT_C</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>order</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>kongfu_min</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>kongfu_max</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>hit_move_ratio</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>玩家武力/主目标武力万分比，下限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>玩家武力/主目标武力万分比，上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>怪物受击被击退的概率万分比</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -93,349 +115,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -443,251 +136,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -696,63 +147,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -801,7 +208,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -834,9 +241,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -869,6 +293,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1030,21 +471,26 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCFF044-6CCF-4197-A8C6-A0E85238FF7A}">
   <dimension ref="A1:D99"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
-    <col min="2" max="3" width="32.875" customWidth="1"/>
-    <col min="4" max="4" width="27.625" customWidth="1"/>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="32.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +498,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" ht="14.25" spans="1:4">
+    <row r="2" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1066,7 +512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1094,7 +540,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1102,18 +548,18 @@
         <v>0</v>
       </c>
       <c r="C5" s="1">
-        <v>4927</v>
+        <v>4926</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
-        <v>4928</v>
+        <v>4927</v>
       </c>
       <c r="C6" s="1">
         <v>4950</v>
@@ -1122,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1136,7 +582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1150,7 +596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1164,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1178,7 +624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1192,7 +638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1206,7 +652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1220,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1234,7 +680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1248,7 +694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1262,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1276,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1290,7 +736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1304,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1318,7 +764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1332,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1346,7 +792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1360,7 +806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1374,7 +820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1388,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1402,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1416,7 +862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1430,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1444,7 +890,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1458,7 +904,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -1472,7 +918,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1486,7 +932,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -1500,7 +946,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -1514,7 +960,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -1528,7 +974,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -1542,7 +988,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -1556,7 +1002,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -1570,7 +1016,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -1584,7 +1030,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -1598,7 +1044,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -1612,7 +1058,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -1626,7 +1072,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -1640,7 +1086,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -1654,7 +1100,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -1668,7 +1114,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -1682,7 +1128,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -1696,7 +1142,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -1710,7 +1156,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -1724,7 +1170,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -1738,7 +1184,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -1752,7 +1198,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -1766,7 +1212,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>49</v>
       </c>
@@ -1780,7 +1226,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50</v>
       </c>
@@ -1794,7 +1240,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>51</v>
       </c>
@@ -1808,7 +1254,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>52</v>
       </c>
@@ -1822,7 +1268,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>53</v>
       </c>
@@ -1836,7 +1282,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>54</v>
       </c>
@@ -1850,7 +1296,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>55</v>
       </c>
@@ -1864,7 +1310,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>56</v>
       </c>
@@ -1878,7 +1324,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>57</v>
       </c>
@@ -1892,7 +1338,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>58</v>
       </c>
@@ -1906,7 +1352,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>59</v>
       </c>
@@ -1920,7 +1366,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>60</v>
       </c>
@@ -1934,7 +1380,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>61</v>
       </c>
@@ -1948,7 +1394,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>62</v>
       </c>
@@ -1962,7 +1408,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>63</v>
       </c>
@@ -1976,7 +1422,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>64</v>
       </c>
@@ -1990,7 +1436,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>65</v>
       </c>
@@ -2004,7 +1450,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>66</v>
       </c>
@@ -2018,7 +1464,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>67</v>
       </c>
@@ -2032,7 +1478,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>68</v>
       </c>
@@ -2046,7 +1492,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>69</v>
       </c>
@@ -2060,7 +1506,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>70</v>
       </c>
@@ -2074,7 +1520,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>71</v>
       </c>
@@ -2088,7 +1534,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>72</v>
       </c>
@@ -2102,7 +1548,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>73</v>
       </c>
@@ -2116,7 +1562,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>74</v>
       </c>
@@ -2130,7 +1576,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>75</v>
       </c>
@@ -2144,7 +1590,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>76</v>
       </c>
@@ -2158,7 +1604,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>77</v>
       </c>
@@ -2172,7 +1618,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>78</v>
       </c>
@@ -2186,7 +1632,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>79</v>
       </c>
@@ -2200,7 +1646,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>80</v>
       </c>
@@ -2214,7 +1660,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>81</v>
       </c>
@@ -2228,7 +1674,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>82</v>
       </c>
@@ -2242,7 +1688,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>83</v>
       </c>
@@ -2256,7 +1702,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>84</v>
       </c>
@@ -2270,7 +1716,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>85</v>
       </c>
@@ -2284,7 +1730,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>86</v>
       </c>
@@ -2298,7 +1744,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>87</v>
       </c>
@@ -2312,7 +1758,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>88</v>
       </c>
@@ -2326,7 +1772,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>89</v>
       </c>
@@ -2340,7 +1786,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>90</v>
       </c>
@@ -2354,7 +1800,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>91</v>
       </c>
@@ -2368,7 +1814,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>92</v>
       </c>
@@ -2382,7 +1828,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>93</v>
       </c>
@@ -2396,7 +1842,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>94</v>
       </c>
@@ -2410,7 +1856,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>95</v>
       </c>
@@ -2425,7 +1871,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>